--- a/CPATPub/main/python/condition0.xlsx
+++ b/CPATPub/main/python/condition0.xlsx
@@ -1,96 +1,48 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PowerSystemLab\Documents\FromDesktop\01_研究資料\05_実行ファイル\CPAT\03_Paid\R06_1.0_GUI_Pub_福井大学（電力システム研究室）\CPATPubR06V1.0\CPATPub\main\python\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2F82D86-0B41-4C00-9BE7-7FFCC4832E27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="9">
-  <si>
-    <t>Time</t>
-  </si>
-  <si>
-    <t>Ktyp</t>
-  </si>
-  <si>
-    <t>Ichi</t>
-  </si>
-  <si>
-    <t>Data1</t>
-  </si>
-  <si>
-    <t>Data2</t>
-  </si>
-  <si>
-    <t>Data3</t>
-  </si>
-  <si>
-    <t>Data4</t>
-  </si>
-  <si>
-    <t>1.0,1.07,1.3,1.06,1.13,1.36</t>
-  </si>
-  <si>
-    <t>G,O,C,G,O,C</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
+      <name val="游ゴシック"/>
+      <charset val="128"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="游ゴシック"/>
-      <family val="2"/>
-      <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="游ゴシック"/>
+      <charset val="128"/>
+      <family val="2"/>
       <sz val="6"/>
-      <name val="游ゴシック"/>
-      <family val="2"/>
-      <charset val="128"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor theme="7" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -105,35 +57,94 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -433,234 +444,302 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:M11"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr codeName="Sheet1">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="23.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.75" style="2" bestFit="1" customWidth="1"/>
+    <col width="23.5" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
+    <col width="12.25" bestFit="1" customWidth="1" style="2" min="2" max="2"/>
+    <col width="16.625" bestFit="1" customWidth="1" style="2" min="3" max="3"/>
+    <col width="11.125" bestFit="1" customWidth="1" style="2" min="4" max="4"/>
+    <col width="12.75" bestFit="1" customWidth="1" style="2" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Ktyp</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Ichi</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Data1</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Data2</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Data3</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Data4</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A2" s="3" t="s">
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>1.0,1.07,1.3,1.06,1.13,1.36</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>G,O,C,G,O,C</t>
+        </is>
+      </c>
+      <c r="C2" s="1">
+        <f>L2 &amp; "," &amp;L2 &amp; "," &amp;L2 &amp; "," &amp;M2 &amp; "," &amp;M2 &amp; "," &amp;M2</f>
+        <v/>
+      </c>
+      <c r="K2" s="3" t="n"/>
+      <c r="L2" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>1.0,1.07,1.3,1.06,1.13,1.36</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>G,O,C,G,O,C</t>
+        </is>
+      </c>
+      <c r="C3" s="1">
+        <f>L3 &amp; "," &amp;L3 &amp; "," &amp;L3 &amp; "," &amp;M3 &amp; "," &amp;M3 &amp; "," &amp;M3</f>
+        <v/>
+      </c>
+      <c r="K3" s="3" t="n"/>
+      <c r="L3" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>1.0,1.07,1.3,1.06,1.13,1.36</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>G,O,C,G,O,C</t>
+        </is>
+      </c>
+      <c r="C4" s="1">
+        <f>L4 &amp; "," &amp;L4 &amp; "," &amp;L4 &amp; "," &amp;M4 &amp; "," &amp;M4 &amp; "," &amp;M4</f>
+        <v/>
+      </c>
+      <c r="K4" s="3" t="n"/>
+      <c r="L4" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>1.89189189</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>1.0,1.07,1.3,1.06,1.13,1.36</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>G,O,C,G,O,C</t>
+        </is>
+      </c>
+      <c r="C5" s="1">
+        <f>L5 &amp; "," &amp;L5 &amp; "," &amp;L5 &amp; "," &amp;M5 &amp; "," &amp;M5 &amp; "," &amp;M5</f>
+        <v/>
+      </c>
+      <c r="K5" s="3" t="n"/>
+      <c r="L5" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="T5" s="3" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>1.0,1.07,1.3,1.06,1.13,1.36</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>G,O,C,G,O,C</t>
+        </is>
+      </c>
+      <c r="C6" s="1">
+        <f>L6 &amp; "," &amp;L6 &amp; "," &amp;L6 &amp; "," &amp;M6 &amp; "," &amp;M6 &amp; "," &amp;M6</f>
+        <v/>
+      </c>
+      <c r="K6" s="3" t="n"/>
+      <c r="L6" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>1.0,1.07,1.3,1.06,1.13,1.36</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>G,O,C,G,O,C</t>
+        </is>
+      </c>
+      <c r="C7" s="1">
+        <f>L7 &amp; "," &amp;L7 &amp; "," &amp;L7 &amp; "," &amp;M7 &amp; "," &amp;M7 &amp; "," &amp;M7</f>
+        <v/>
+      </c>
+      <c r="K7" s="3" t="n"/>
+      <c r="L7" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>1.0,1.07,1.3,1.06,1.13,1.36</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>G,O,C,G,O,C</t>
+        </is>
+      </c>
+      <c r="C8" s="1">
+        <f>L8 &amp; "," &amp;L8 &amp; "," &amp;L8 &amp; "," &amp;M8 &amp; "," &amp;M8 &amp; "," &amp;M8</f>
+        <v/>
+      </c>
+      <c r="K8" s="3" t="n"/>
+      <c r="L8" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="M8" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="1" t="str">
-        <f t="shared" ref="C2:C11" si="0">L2 &amp; "," &amp;L2 &amp; "," &amp;L2 &amp; "," &amp;M2 &amp; "," &amp;M2 &amp; "," &amp;M2</f>
-        <v>55,55,55,54,54,54</v>
-      </c>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3">
-        <v>55</v>
-      </c>
-      <c r="M2" s="3">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>26,26,26,32,32,32</v>
-      </c>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3">
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>1.0,1.07,1.3,1.06,1.13,1.36</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>G,O,C,G,O,C</t>
+        </is>
+      </c>
+      <c r="C9" s="1">
+        <f>L9 &amp; "," &amp;L9 &amp; "," &amp;L9 &amp; "," &amp;M9 &amp; "," &amp;M9 &amp; "," &amp;M9</f>
+        <v/>
+      </c>
+      <c r="K9" s="3" t="n"/>
+      <c r="L9" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>1.0,1.07,1.3,1.06,1.13,1.36</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>G,O,C,G,O,C</t>
+        </is>
+      </c>
+      <c r="C10" s="1">
+        <f>L10 &amp; "," &amp;L10 &amp; "," &amp;L10 &amp; "," &amp;M10 &amp; "," &amp;M10 &amp; "," &amp;M10</f>
+        <v/>
+      </c>
+      <c r="K10" s="3" t="n"/>
+      <c r="L10" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="M10" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="M3" s="3">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>25,25,25,24,24,24</v>
-      </c>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3">
-        <v>25</v>
-      </c>
-      <c r="M4" s="3">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>12,12,12,19,19,19</v>
-      </c>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3">
-        <v>12</v>
-      </c>
-      <c r="M5" s="3">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>54,54,54,27,27,27</v>
-      </c>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3">
-        <v>54</v>
-      </c>
-      <c r="M6" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>28,28,28,12,12,12</v>
-      </c>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3">
-        <v>28</v>
-      </c>
-      <c r="M7" s="3">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A8" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>55,55,55,7,7,7</v>
-      </c>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3">
-        <v>55</v>
-      </c>
-      <c r="M8" s="3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A9" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>13,13,13,35,35,35</v>
-      </c>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3">
-        <v>13</v>
-      </c>
-      <c r="M9" s="3">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A10" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>11,11,11,26,26,26</v>
-      </c>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3">
-        <v>11</v>
-      </c>
-      <c r="M10" s="3">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A11" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>14,14,14,31,31,31</v>
-      </c>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3">
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>1.0,1.07,1.3,1.06,1.13,1.36</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>G,O,C,G,O,C</t>
+        </is>
+      </c>
+      <c r="C11" s="1">
+        <f>L11 &amp; "," &amp;L11 &amp; "," &amp;L11 &amp; "," &amp;M11 &amp; "," &amp;M11 &amp; "," &amp;M11</f>
+        <v/>
+      </c>
+      <c r="K11" s="3" t="n"/>
+      <c r="L11" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="M11" s="3">
+      <c r="M11" s="3" t="n">
         <v>31</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>